--- a/research/traditional_assets/database/data/romania/romania_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_engineering_construction.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,23 +587,26 @@
           <t>Engineering/Construction</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.18535</v>
+      </c>
       <c r="G2">
-        <v>-1.673913043478261</v>
+        <v>-0.4020141814818621</v>
       </c>
       <c r="H2">
-        <v>-1.673913043478261</v>
+        <v>-0.4020141814818621</v>
       </c>
       <c r="I2">
-        <v>-3.007246376811594</v>
+        <v>-0.1628815126913986</v>
       </c>
       <c r="J2">
-        <v>-3.007246376811594</v>
+        <v>-0.1357345939094989</v>
       </c>
       <c r="K2">
-        <v>-0.31</v>
+        <v>-2.444</v>
       </c>
       <c r="L2">
-        <v>-0.5615942028985507</v>
+        <v>-0.2511560990648443</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,70 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.17</v>
+        <v>5.4</v>
       </c>
       <c r="V2">
-        <v>1.411338962605549</v>
+        <v>1.904761904761905</v>
       </c>
       <c r="W2">
-        <v>0.1183206106870229</v>
+        <v>-0.1452581032412965</v>
       </c>
       <c r="X2">
-        <v>0.4216911139440034</v>
+        <v>0.1137634365247258</v>
       </c>
       <c r="Y2">
-        <v>-0.3033705032569806</v>
+        <v>-0.2590215397660223</v>
       </c>
       <c r="Z2">
-        <v>0.1467304625199362</v>
+        <v>0.8662097204913655</v>
       </c>
       <c r="AA2">
-        <v>-0.4412546517809676</v>
+        <v>-0.163769211388259</v>
       </c>
       <c r="AB2">
-        <v>0.08133538568931266</v>
+        <v>0.1114590751848049</v>
       </c>
       <c r="AC2">
-        <v>-0.5225900374702803</v>
+        <v>-0.2752282865730639</v>
       </c>
       <c r="AD2">
-        <v>6.7</v>
+        <v>4.949</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.7</v>
+        <v>4.949</v>
       </c>
       <c r="AG2">
-        <v>5.53</v>
+        <v>-0.4510000000000005</v>
       </c>
       <c r="AH2">
-        <v>0.8898924159914996</v>
+        <v>0.6357913669064749</v>
       </c>
       <c r="AI2">
-        <v>1.903409090909091</v>
+        <v>0.5190895741556535</v>
       </c>
       <c r="AJ2">
-        <v>0.8696335901871364</v>
+        <v>-0.1891778523489935</v>
       </c>
       <c r="AK2">
-        <v>2.353191489361702</v>
+        <v>-0.1090953072085149</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AM2">
-        <v>-0.001</v>
+        <v>0.023</v>
       </c>
       <c r="AN2">
-        <v>-4.379084967320262</v>
+        <v>-10.7353579175705</v>
+      </c>
+      <c r="AO2">
+        <v>-52.83333333333334</v>
       </c>
       <c r="AP2">
-        <v>-3.61437908496732</v>
+        <v>0.9783080260303699</v>
       </c>
       <c r="AQ2">
-        <v>1660</v>
+        <v>-68.91304347826087</v>
       </c>
     </row>
     <row r="3">
@@ -710,22 +716,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-1.673913043478261</v>
+        <v>2.836363636363636</v>
       </c>
       <c r="H3">
-        <v>-1.673913043478261</v>
+        <v>2.836363636363636</v>
       </c>
       <c r="I3">
-        <v>-3.007246376811594</v>
+        <v>-0.2318181818181818</v>
       </c>
       <c r="J3">
-        <v>-3.007246376811594</v>
+        <v>-0.1159090909090909</v>
       </c>
       <c r="K3">
-        <v>-0.31</v>
+        <v>-1</v>
       </c>
       <c r="L3">
-        <v>-0.5615942028985507</v>
+        <v>-4.545454545454546</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,70 +755,320 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.17</v>
+        <v>3.95</v>
       </c>
       <c r="V3">
-        <v>1.411338962605549</v>
+        <v>7.995951417004049</v>
       </c>
       <c r="W3">
-        <v>0.1183206106870229</v>
+        <v>0.3144654088050314</v>
       </c>
       <c r="X3">
-        <v>0.4216911139440034</v>
+        <v>0.6959394718404517</v>
       </c>
       <c r="Y3">
-        <v>-0.3033705032569806</v>
+        <v>-0.3814740630354203</v>
       </c>
       <c r="Z3">
-        <v>0.1467304625199362</v>
+        <v>0.09361702127659574</v>
       </c>
       <c r="AA3">
-        <v>-0.4412546517809676</v>
+        <v>-0.01085106382978723</v>
       </c>
       <c r="AB3">
-        <v>0.08133538568931266</v>
+        <v>0.1299856524754085</v>
       </c>
       <c r="AC3">
-        <v>-0.5225900374702803</v>
+        <v>-0.1408367163051957</v>
       </c>
       <c r="AD3">
-        <v>6.7</v>
+        <v>4.82</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.7</v>
+        <v>4.82</v>
       </c>
       <c r="AG3">
-        <v>5.53</v>
+        <v>0.8700000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.8898924159914996</v>
+        <v>0.907038012796387</v>
       </c>
       <c r="AI3">
-        <v>1.903409090909091</v>
+        <v>1.133584195672624</v>
       </c>
       <c r="AJ3">
-        <v>0.8696335901871364</v>
+        <v>0.6378299120234604</v>
       </c>
       <c r="AK3">
-        <v>2.353191489361702</v>
+        <v>2.880794701986754</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.001</v>
+        <v>-0.007</v>
       </c>
       <c r="AN3">
-        <v>-4.379084967320262</v>
+        <v>14.05247813411079</v>
       </c>
       <c r="AP3">
-        <v>-3.61437908496732</v>
+        <v>2.536443148688047</v>
       </c>
       <c r="AQ3">
-        <v>1660</v>
+        <v>7.285714285714285</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Societatea de Constructii Napoca SA (BVB:NAPO)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Engineering/Construction</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0387</v>
+      </c>
+      <c r="G4">
+        <v>-0.4433862433862434</v>
+      </c>
+      <c r="H4">
+        <v>-0.4433862433862434</v>
+      </c>
+      <c r="I4">
+        <v>-0.1375661375661376</v>
+      </c>
+      <c r="J4">
+        <v>-0.1375661375661376</v>
+      </c>
+      <c r="K4">
+        <v>-1.21</v>
+      </c>
+      <c r="L4">
+        <v>-0.128042328042328</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1.41</v>
+      </c>
+      <c r="V4">
+        <v>0.6380090497737556</v>
+      </c>
+      <c r="W4">
+        <v>-0.1452581032412965</v>
+      </c>
+      <c r="X4">
+        <v>0.1137634365247258</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2590215397660223</v>
+      </c>
+      <c r="Z4">
+        <v>1.19047619047619</v>
+      </c>
+      <c r="AA4">
+        <v>-0.163769211388259</v>
+      </c>
+      <c r="AB4">
+        <v>0.1114590751848049</v>
+      </c>
+      <c r="AC4">
+        <v>-0.2752282865730639</v>
+      </c>
+      <c r="AD4">
+        <v>0.129</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.129</v>
+      </c>
+      <c r="AG4">
+        <v>-1.281</v>
+      </c>
+      <c r="AH4">
+        <v>0.05515177426250534</v>
+      </c>
+      <c r="AI4">
+        <v>0.02835788085293471</v>
+      </c>
+      <c r="AJ4">
+        <v>-1.378902045209903</v>
+      </c>
+      <c r="AK4">
+        <v>-0.4080917489646383</v>
+      </c>
+      <c r="AL4">
+        <v>0.03</v>
+      </c>
+      <c r="AM4">
+        <v>0.03</v>
+      </c>
+      <c r="AN4">
+        <v>-0.2118226600985222</v>
+      </c>
+      <c r="AO4">
+        <v>-43.33333333333334</v>
+      </c>
+      <c r="AP4">
+        <v>2.103448275862069</v>
+      </c>
+      <c r="AQ4">
+        <v>-43.33333333333334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Compania Energopetrol S.A. (BVB:ENP)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Engineering/Construction</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.332</v>
+      </c>
+      <c r="G5">
+        <v>-5.672131147540983</v>
+      </c>
+      <c r="H5">
+        <v>-5.672131147540983</v>
+      </c>
+      <c r="I5">
+        <v>-3.836065573770492</v>
+      </c>
+      <c r="J5">
+        <v>-3.836065573770492</v>
+      </c>
+      <c r="K5">
+        <v>-0.234</v>
+      </c>
+      <c r="L5">
+        <v>-3.836065573770492</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.04</v>
+      </c>
+      <c r="V5">
+        <v>0.3053435114503817</v>
+      </c>
+      <c r="W5">
+        <v>-0.2271844660194175</v>
+      </c>
+      <c r="X5">
+        <v>0.1102596502353577</v>
+      </c>
+      <c r="Y5">
+        <v>-0.3374441162547752</v>
+      </c>
+      <c r="Z5">
+        <v>0.06448202959830866</v>
+      </c>
+      <c r="AA5">
+        <v>-0.2473572938689218</v>
+      </c>
+      <c r="AB5">
+        <v>0.1102596502353577</v>
+      </c>
+      <c r="AC5">
+        <v>-0.3576169441042795</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-0.04</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.4395604395604396</v>
+      </c>
+      <c r="AK5">
+        <v>-0.05772005772005773</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>-0</v>
+      </c>
+      <c r="AP5">
+        <v>0.2051282051282051</v>
       </c>
     </row>
   </sheetData>
